--- a/esyluban/examples/release/DataTables/clothes/套装表.xlsx
+++ b/esyluban/examples/release/DataTables/clothes/套装表.xlsx
@@ -3304,8 +3304,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="U2:X2"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="I1:T1"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="I3:T3"/>
     <mergeCell ref="I2:T2"/>
   </mergeCells>
   <conditionalFormatting sqref="Q4:T6">
